--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.59380725451277</v>
+        <v>7.246493678858325</v>
       </c>
       <c r="D2" t="n">
-        <v>42.30084054851758</v>
+        <v>6.873886589134107</v>
       </c>
       <c r="E2" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F2" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.47388986864064</v>
+        <v>7.227007103654104</v>
       </c>
       <c r="D3" t="n">
-        <v>43.90503584091558</v>
+        <v>7.134568324148782</v>
       </c>
       <c r="E3" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F3" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.47323478542556</v>
+        <v>2.351900652631653</v>
       </c>
       <c r="D4" t="n">
-        <v>13.93810385806052</v>
+        <v>2.264941876934835</v>
       </c>
       <c r="E4" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F4" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.41586722567052</v>
+        <v>4.617578424171461</v>
       </c>
       <c r="D5" t="n">
-        <v>26.16295090390226</v>
+        <v>4.251479521884117</v>
       </c>
       <c r="E5" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F5" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.84637571897242</v>
+        <v>6.637536054333018</v>
       </c>
       <c r="D6" t="n">
-        <v>40.26707654268689</v>
+        <v>6.543399938186621</v>
       </c>
       <c r="E6" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F6" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.133394674641566</v>
+        <v>0.9966766346292545</v>
       </c>
       <c r="D7" t="n">
-        <v>6.274831705963246</v>
+        <v>1.019660152219027</v>
       </c>
       <c r="E7" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F7" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.52835060722726</v>
+        <v>4.14835697367443</v>
       </c>
       <c r="D8" t="n">
-        <v>25.18993018821834</v>
+        <v>4.09336365558548</v>
       </c>
       <c r="E8" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F8" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.01780603341706</v>
+        <v>1.627893480430272</v>
       </c>
       <c r="D9" t="n">
-        <v>11.01135777277262</v>
+        <v>1.789345638075551</v>
       </c>
       <c r="E9" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F9" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.41631473540501</v>
+        <v>4.617651144503315</v>
       </c>
       <c r="D10" t="n">
-        <v>28.2861559981312</v>
+        <v>4.59650034969632</v>
       </c>
       <c r="E10" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F10" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.08197095243672</v>
+        <v>3.588320279770968</v>
       </c>
       <c r="D11" t="n">
-        <v>21.83923164092291</v>
+        <v>3.548875141649973</v>
       </c>
       <c r="E11" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F11" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.80409350236241</v>
+        <v>4.030665194133891</v>
       </c>
       <c r="D12" t="n">
-        <v>25.11458037780643</v>
+        <v>4.081119311393546</v>
       </c>
       <c r="E12" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F12" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.86947294619605</v>
+        <v>5.341289353756859</v>
       </c>
       <c r="D13" t="n">
-        <v>32.58726322434887</v>
+        <v>5.295430273956693</v>
       </c>
       <c r="E13" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F13" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.90730754405105</v>
+        <v>5.672437475908296</v>
       </c>
       <c r="D14" t="n">
-        <v>35.19866505856</v>
+        <v>5.719783072016</v>
       </c>
       <c r="E14" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F14" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>19.15949583827524</v>
+        <v>3.113418073719726</v>
       </c>
       <c r="D15" t="n">
-        <v>19.41264754119399</v>
+        <v>3.154555225444023</v>
       </c>
       <c r="E15" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F15" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>20.27614514961476</v>
+        <v>3.294873586812399</v>
       </c>
       <c r="D16" t="n">
-        <v>19.96445505606342</v>
+        <v>3.244223946610306</v>
       </c>
       <c r="E16" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F16" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>29.66097693011551</v>
+        <v>4.81990875114377</v>
       </c>
       <c r="D17" t="n">
-        <v>29.34769678911968</v>
+        <v>4.769000728231949</v>
       </c>
       <c r="E17" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F17" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39.57138187245828</v>
+        <v>6.430349554274471</v>
       </c>
       <c r="D18" t="n">
-        <v>39.25885211973085</v>
+        <v>6.379563469456264</v>
       </c>
       <c r="E18" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F18" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>35.26751901632424</v>
+        <v>5.730971840152689</v>
       </c>
       <c r="D19" t="n">
-        <v>35.42413400420843</v>
+        <v>5.75642177568387</v>
       </c>
       <c r="E19" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F19" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>47.04629407851255</v>
+        <v>7.64502278775829</v>
       </c>
       <c r="D20" t="n">
-        <v>46.73349993843659</v>
+        <v>7.594193739995946</v>
       </c>
       <c r="E20" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F20" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>27.44680843803666</v>
+        <v>4.460106371180957</v>
       </c>
       <c r="D21" t="n">
-        <v>27.33184134187362</v>
+        <v>4.441424218054463</v>
       </c>
       <c r="E21" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F21" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>36.3493256967275</v>
+        <v>5.906765425718219</v>
       </c>
       <c r="D22" t="n">
-        <v>36.39584258240136</v>
+        <v>5.914324419640222</v>
       </c>
       <c r="E22" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F22" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>43.00984510655719</v>
+        <v>6.989099829815543</v>
       </c>
       <c r="D23" t="n">
-        <v>42.96171209521254</v>
+        <v>6.981278215472038</v>
       </c>
       <c r="E23" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F23" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>38.19839773418941</v>
+        <v>6.207239631805779</v>
       </c>
       <c r="D24" t="n">
-        <v>38.07098234229095</v>
+        <v>6.186534630622279</v>
       </c>
       <c r="E24" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F24" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>41.39094364371272</v>
+        <v>6.726028342103317</v>
       </c>
       <c r="D25" t="n">
-        <v>41.2162025382455</v>
+        <v>6.697632912464893</v>
       </c>
       <c r="E25" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F25" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>46.63564934769023</v>
+        <v>7.578293018999662</v>
       </c>
       <c r="D26" t="n">
-        <v>46.43346459966504</v>
+        <v>7.545437997445569</v>
       </c>
       <c r="E26" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F26" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>17.52838016465555</v>
+        <v>2.848361776756527</v>
       </c>
       <c r="D27" t="n">
-        <v>17.44810042916257</v>
+        <v>2.835316319738918</v>
       </c>
       <c r="E27" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F27" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>9.980259130612039</v>
+        <v>1.621792108724456</v>
       </c>
       <c r="D28" t="n">
-        <v>9.91828017579175</v>
+        <v>1.61172052856616</v>
       </c>
       <c r="E28" t="n">
-        <v>11.80919525612649</v>
+        <v>1.918994229120555</v>
       </c>
       <c r="F28" t="n">
-        <v>11.61156213236702</v>
+        <v>1.886878846509641</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
